--- a/static/data/exports/Retro_TR_GE_2024.xlsx
+++ b/static/data/exports/Retro_TR_GE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_TR_GE_2024.xlsx
+++ b/static/data/exports/Retro_TR_GE_2024.xlsx
@@ -3197,20 +3197,20 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1780940</v>
+        <v>1780939</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ramendra Reang</t>
+          <t>Arun Kumar Bhaumik</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SUCI</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>22919</v>
+        <v>22920</v>
       </c>
       <c r="E45" t="n">
         <v>299</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Ramendra Reang</t>
+          <t>Arun Kumar Bhaumik</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SUCI</t>
         </is>
       </c>
       <c r="Q45" t="b">
@@ -3259,20 +3259,20 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1780939</v>
+        <v>1780940</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arun Kumar Bhaumik</t>
+          <t>Ramendra Reang</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SUCI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>22920</v>
+        <v>22919</v>
       </c>
       <c r="E46" t="n">
         <v>299</v>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Arun Kumar Bhaumik</t>
+          <t>Ramendra Reang</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>SUCI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q46" t="b">
